--- a/data/trans_orig/Q5404-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q5404-Habitat-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de manejar dinero en 2007</t>
+          <t>Población según si es capaz de manejar dinero en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6678</t>
+          <t>7543</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>6,56%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3460</t>
+          <t>3417</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15669</t>
+          <t>15462</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,48%</t>
+          <t>10,34%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4936</t>
+          <t>4926</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>18239</t>
+          <t>17947</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,87%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,9%</t>
+          <t>6,78%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5485</t>
+          <t>5594</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>16974</t>
+          <t>18082</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,77%</t>
+          <t>4,87%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>14,76%</t>
+          <t>15,73%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1970</t>
+          <t>1976</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11624</t>
+          <t>11862</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8749</t>
+          <t>8656</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23891</t>
+          <t>23975</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,31%</t>
+          <t>3,27%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,03%</t>
+          <t>9,06%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>95675</t>
+          <t>95485</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>108387</t>
+          <t>107786</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>83,04%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>94,26%</t>
+          <t>93,74%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>127754</t>
+          <t>127274</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>141985</t>
+          <t>142792</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>85,43%</t>
+          <t>85,11%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>94,95%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>227989</t>
+          <t>228551</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>248029</t>
+          <t>247915</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>86,19%</t>
+          <t>86,4%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>93,76%</t>
+          <t>93,72%</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6420</t>
+          <t>6348</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,35%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2182</t>
+          <t>2310</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13544</t>
+          <t>15056</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3250</t>
+          <t>3182</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>15766</t>
+          <t>14646</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,97%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,46%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>928</t>
+          <t>930</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8482</t>
+          <t>8668</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1322,7 +1322,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,81%</t>
+          <t>5,94%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3763</t>
+          <t>3528</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>15554</t>
+          <t>17117</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>8,51%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6485</t>
+          <t>6561</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>21232</t>
+          <t>21727</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1387,12 +1387,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,46%</t>
+          <t>6,61%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>134780</t>
+          <t>133781</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>143247</t>
+          <t>143244</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,7 +1430,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>92,39%</t>
+          <t>91,7%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>159329</t>
+          <t>158122</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>174792</t>
+          <t>174721</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>87,22%</t>
+          <t>86,56%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,68%</t>
+          <t>95,64%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>299012</t>
+          <t>298957</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>316540</t>
+          <t>317003</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>91,0%</t>
+          <t>90,99%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,34%</t>
+          <t>96,48%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>829</t>
+          <t>751</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>9992</t>
+          <t>10216</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,57%</t>
+          <t>9,79%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2752</t>
+          <t>2393</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>14499</t>
+          <t>13096</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>1,76%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4880</t>
+          <t>4896</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>18452</t>
+          <t>18404</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,04%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,68%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5644</t>
+          <t>5708</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2168</t>
+          <t>2679</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>11838</t>
+          <t>12395</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,97%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>8,71%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3655</t>
+          <t>3689</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>13511</t>
+          <t>14389</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,54%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>92649</t>
+          <t>92639</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>102566</t>
+          <t>102534</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,77%</t>
+          <t>88,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,27%</t>
+          <t>98,24%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>114738</t>
+          <t>114901</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>129285</t>
+          <t>129141</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,46%</t>
+          <t>84,58%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,17%</t>
+          <t>95,06%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>213350</t>
+          <t>212020</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>229045</t>
+          <t>229371</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,81%</t>
+          <t>88,26%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,48%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>827</t>
+          <t>835</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7638</t>
+          <t>7609</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2116,12 +2116,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,6%</t>
+          <t>0,61%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3402</t>
+          <t>3867</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>14959</t>
+          <t>15889</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,17%</t>
+          <t>7,61%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6698</t>
+          <t>6319</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19847</t>
+          <t>19834</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,94%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,74%</t>
+          <t>5,73%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>1682</t>
+          <t>2440</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10222</t>
+          <t>10861</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,45%</t>
+          <t>7,92%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8186</t>
+          <t>8033</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23354</t>
+          <t>22737</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,92%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>11,19%</t>
+          <t>10,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11920</t>
+          <t>12126</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>29578</t>
+          <t>29394</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,45%</t>
+          <t>3,5%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,5%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>122325</t>
+          <t>122947</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>133074</t>
+          <t>132988</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>89,15%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>96,98%</t>
+          <t>96,92%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>175127</t>
+          <t>176313</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>193882</t>
+          <t>193704</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>83,88%</t>
+          <t>84,45%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,78%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>303348</t>
+          <t>303743</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>324866</t>
+          <t>324125</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,79%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>93,89%</t>
+          <t>93,68%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5317</t>
+          <t>5392</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>18015</t>
+          <t>19218</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2572,12 +2572,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,59%</t>
+          <t>3,82%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>19218</t>
+          <t>19259</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>41045</t>
+          <t>40464</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,84%</t>
+          <t>2,85%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>6,06%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>27873</t>
+          <t>28782</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>53769</t>
+          <t>55118</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,56%</t>
+          <t>4,67%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13916</t>
+          <t>13308</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>31602</t>
+          <t>29910</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,65%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,29%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>24032</t>
+          <t>24356</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>47431</t>
+          <t>47509</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>41916</t>
+          <t>42763</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>69174</t>
+          <t>70900</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,55%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>6,01%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>457783</t>
+          <t>459469</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>480232</t>
+          <t>480326</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>91,11%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>95,58%</t>
+          <t>95,59%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>597619</t>
+          <t>597520</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>627669</t>
+          <t>628825</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>88,3%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>92,73%</t>
+          <t>92,91%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1064244</t>
+          <t>1062788</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1102137</t>
+          <t>1102062</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>90,24%</t>
+          <t>90,12%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>93,46%</t>
+          <t>93,45%</t>
         </is>
       </c>
     </row>
@@ -3050,7 +3050,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de manejar dinero en 2012</t>
+          <t>Población según si es capaz de manejar dinero en 2012 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1921</t>
+          <t>1920</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>11816</t>
+          <t>10970</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3265,7 +3265,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>8,47%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4248</t>
+          <t>4234</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16205</t>
+          <t>16275</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,54%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,76%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7362</t>
+          <t>7544</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>22541</t>
+          <t>21920</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,16%</t>
         </is>
       </c>
     </row>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13473</t>
+          <t>13236</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,65%</t>
+          <t>9,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10363</t>
+          <t>10450</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26461</t>
+          <t>26918</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,21%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>15,87%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12122</t>
+          <t>12957</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31984</t>
+          <t>31007</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,23%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,44%</t>
+          <t>10,12%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>121508</t>
+          <t>122156</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>135447</t>
+          <t>136193</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>87,07%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,06%</t>
+          <t>97,6%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>130693</t>
+          <t>130335</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>149414</t>
+          <t>149234</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,48%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>259275</t>
+          <t>261199</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>283360</t>
+          <t>282053</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>84,64%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>92,5%</t>
+          <t>92,07%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2214</t>
+          <t>2244</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13238</t>
+          <t>13842</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,55%</t>
+          <t>8,94%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8420</t>
+          <t>8762</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>24268</t>
+          <t>23876</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,4%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,68%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>13838</t>
+          <t>14074</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>32890</t>
+          <t>32253</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,5%</t>
+          <t>9,31%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7949</t>
+          <t>7849</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24640</t>
+          <t>24898</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3829,12 +3829,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>5,13%</t>
+          <t>5,07%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>15,91%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>18664</t>
+          <t>17511</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>37952</t>
+          <t>39654</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,15%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>19,83%</t>
+          <t>20,72%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>29133</t>
+          <t>29914</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>55211</t>
+          <t>55473</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,41%</t>
+          <t>8,64%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>15,94%</t>
+          <t>16,02%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>123124</t>
+          <t>123195</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>142084</t>
+          <t>141616</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>79,5%</t>
+          <t>79,54%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,74%</t>
+          <t>91,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>136365</t>
+          <t>136849</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>160008</t>
+          <t>161698</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>71,24%</t>
+          <t>71,49%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>83,59%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>268425</t>
+          <t>266866</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>299267</t>
+          <t>297174</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>77,51%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>86,42%</t>
+          <t>85,81%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2207</t>
+          <t>2123</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15607</t>
+          <t>15309</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,13%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>14,78%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4420</t>
+          <t>4798</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18289</t>
+          <t>18567</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,13%</t>
+          <t>3,4%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>12,97%</t>
+          <t>13,17%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>8831</t>
+          <t>8533</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>27064</t>
+          <t>27817</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,61%</t>
+          <t>3,49%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,06%</t>
+          <t>11,37%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>956</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8310</t>
+          <t>8629</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,0%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,02%</t>
+          <t>8,33%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9601</t>
+          <t>9610</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25601</t>
+          <t>25764</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4325,7 +4325,7 @@
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,15%</t>
+          <t>18,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11826</t>
+          <t>11515</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28273</t>
+          <t>28627</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,83%</t>
+          <t>4,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,56%</t>
+          <t>11,7%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>85621</t>
+          <t>85132</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>99404</t>
+          <t>99529</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>95,95%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>103499</t>
+          <t>104093</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>123233</t>
+          <t>123719</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,39%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,73%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>196292</t>
+          <t>195333</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>219518</t>
+          <t>219590</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,74%</t>
+          <t>89,77%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>1937</t>
+          <t>2018</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>10955</t>
+          <t>11516</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>7080</t>
+          <t>6375</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20992</t>
+          <t>20543</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,61%</t>
+          <t>8,43%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10745</t>
+          <t>10394</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26487</t>
+          <t>26759</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,6%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4171</t>
+          <t>4040</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>18120</t>
+          <t>17468</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4741,12 +4741,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,58%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>10,81%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9187</t>
+          <t>9064</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26243</t>
+          <t>24631</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>3,72%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,1%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>16320</t>
+          <t>17376</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>37753</t>
+          <t>37825</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,03%</t>
+          <t>4,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,33%</t>
         </is>
       </c>
     </row>
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>137714</t>
+          <t>137806</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>153383</t>
+          <t>154044</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>85,21%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>94,91%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>203595</t>
+          <t>204006</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>224746</t>
+          <t>223756</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>83,53%</t>
+          <t>83,69%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>92,2%</t>
+          <t>91,8%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>349119</t>
+          <t>347589</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>374722</t>
+          <t>373201</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>86,12%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>92,44%</t>
+          <t>92,07%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>14513</t>
+          <t>13843</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>35101</t>
+          <t>33816</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,04%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>33631</t>
+          <t>34137</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>61169</t>
+          <t>60379</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,53%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,23%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>54235</t>
+          <t>54167</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>87573</t>
+          <t>87626</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5159,7 +5159,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,72%</t>
+          <t>6,73%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>20052</t>
+          <t>19699</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>45463</t>
+          <t>44532</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,52%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>8,12%</t>
+          <t>7,96%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>60104</t>
+          <t>60606</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>93293</t>
+          <t>95705</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>8,16%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,56%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>86442</t>
+          <t>87021</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>127076</t>
+          <t>128747</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,64%</t>
+          <t>6,68%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,88%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>488260</t>
+          <t>490400</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>519724</t>
+          <t>520596</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>87,25%</t>
+          <t>87,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>93,02%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>597793</t>
+          <t>598491</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>641081</t>
+          <t>639661</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>80,46%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,09%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1103585</t>
+          <t>1098264</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1153991</t>
+          <t>1152995</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,31%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>88,59%</t>
+          <t>88,51%</t>
         </is>
       </c>
     </row>
@@ -5562,7 +5562,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de manejar dinero en 2016</t>
+          <t>Población según si es capaz de manejar dinero en 2016 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1800</t>
+          <t>1764</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10426</t>
+          <t>10272</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,29%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1820</t>
+          <t>1119</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11132</t>
+          <t>11062</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>1,05%</t>
+          <t>0,65%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4607</t>
+          <t>4970</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17081</t>
+          <t>17430</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,51%</t>
+          <t>5,62%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1571</t>
+          <t>1580</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8755</t>
+          <t>10120</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>7,4%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4854</t>
+          <t>4562</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>18895</t>
+          <t>17580</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,9%</t>
+          <t>10,14%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8264</t>
+          <t>8356</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23835</t>
+          <t>23757</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>7,69%</t>
+          <t>7,66%</t>
         </is>
       </c>
     </row>
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>121284</t>
+          <t>121221</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>132044</t>
+          <t>131858</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>88,7%</t>
+          <t>88,65%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>96,57%</t>
+          <t>96,43%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>149637</t>
+          <t>149306</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>165163</t>
+          <t>165115</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>86,3%</t>
+          <t>86,11%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>95,25%</t>
+          <t>95,23%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>275200</t>
+          <t>275198</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>294504</t>
+          <t>294719</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6073,7 +6073,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>94,96%</t>
+          <t>95,03%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1682</t>
+          <t>1673</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9952</t>
+          <t>9818</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,01%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,95%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1281</t>
+          <t>1245</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>14398</t>
+          <t>13882</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>0,57%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,57%</t>
+          <t>6,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4244</t>
+          <t>4142</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>19016</t>
+          <t>19958</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,95%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1639</t>
+          <t>1651</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8422</t>
+          <t>9264</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,11%</t>
+          <t>5,62%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>8355</t>
+          <t>7279</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>24351</t>
+          <t>23605</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>10,77%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>11440</t>
+          <t>10503</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>28915</t>
+          <t>29107</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,58%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>150367</t>
+          <t>149949</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>160710</t>
+          <t>160575</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,43%</t>
+          <t>97,35%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>187436</t>
+          <t>189045</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>207179</t>
+          <t>208350</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>85,52%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>94,53%</t>
+          <t>95,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>343745</t>
+          <t>344171</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>365514</t>
+          <t>366034</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,49%</t>
+          <t>89,6%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,16%</t>
+          <t>95,3%</t>
         </is>
       </c>
     </row>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>3281</t>
+          <t>4062</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6689,7 +6689,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>3,53%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2587</t>
+          <t>2616</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>15038</t>
+          <t>14272</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,55%</t>
+          <t>10,01%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3493</t>
+          <t>3651</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>15981</t>
+          <t>16612</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,2%</t>
+          <t>6,45%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>1878</t>
+          <t>2044</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11173</t>
+          <t>11762</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>10,22%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6373</t>
+          <t>6421</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21561</t>
+          <t>21867</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,47%</t>
+          <t>4,5%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>15,33%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11462</t>
+          <t>10803</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>29319</t>
+          <t>28623</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,38%</t>
+          <t>11,11%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>103173</t>
+          <t>101966</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>112488</t>
+          <t>112156</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>88,64%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,79%</t>
+          <t>97,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>112307</t>
+          <t>111887</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>130702</t>
+          <t>130666</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,76%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,66%</t>
+          <t>91,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>219201</t>
+          <t>219062</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>240476</t>
+          <t>239380</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,08%</t>
+          <t>85,03%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>93,34%</t>
+          <t>92,92%</t>
         </is>
       </c>
     </row>
@@ -7125,12 +7125,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>1754</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -7140,12 +7140,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5205</t>
+          <t>5008</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20586</t>
+          <t>20830</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,14%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>8,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5238</t>
+          <t>5169</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21124</t>
+          <t>21774</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,06%</t>
+          <t>5,22%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3089</t>
+          <t>3098</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12856</t>
+          <t>13577</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7258,7 +7258,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>7,78%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5911</t>
+          <t>5854</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21029</t>
+          <t>21582</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,43%</t>
+          <t>2,41%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,89%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11130</t>
+          <t>11703</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>30272</t>
+          <t>29968</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,67%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,18%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>161762</t>
+          <t>161041</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>171529</t>
+          <t>171520</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,7 +7366,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>92,64%</t>
+          <t>92,22%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>207794</t>
+          <t>205816</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>228870</t>
+          <t>228534</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>85,59%</t>
+          <t>84,77%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>94,27%</t>
+          <t>94,13%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>373507</t>
+          <t>373446</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>397481</t>
+          <t>397018</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,12%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5131</t>
+          <t>5304</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17152</t>
+          <t>17202</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,9%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>18963</t>
+          <t>18178</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>43905</t>
+          <t>42735</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,64%</t>
+          <t>5,49%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>27935</t>
+          <t>26846</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>55570</t>
+          <t>54224</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,96%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>3,96%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13451</t>
+          <t>13687</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>31304</t>
+          <t>30963</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,27%</t>
+          <t>2,31%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,29%</t>
+          <t>5,24%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>35064</t>
+          <t>35940</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>64272</t>
+          <t>67382</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,51%</t>
+          <t>4,62%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,26%</t>
+          <t>8,66%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>54949</t>
+          <t>53558</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>88027</t>
+          <t>88741</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,01%</t>
+          <t>3,91%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,48%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>549089</t>
+          <t>549165</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>569142</t>
+          <t>568723</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>92,86%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>96,25%</t>
+          <t>96,18%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>680141</t>
+          <t>679022</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>718071</t>
+          <t>717207</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>87,43%</t>
+          <t>87,29%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>92,31%</t>
+          <t>92,19%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1238855</t>
+          <t>1240146</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1281396</t>
+          <t>1282104</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>90,48%</t>
+          <t>90,57%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>93,58%</t>
+          <t>93,63%</t>
         </is>
       </c>
     </row>
@@ -8074,7 +8074,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si es capaz de manejar dinero en 2023</t>
+          <t>Población según si es capaz de manejar dinero en 2023 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -8269,12 +8269,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>358</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>3744</t>
+          <t>4142</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -8284,12 +8284,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8304,12 +8304,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4811</t>
+          <t>5147</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11694</t>
+          <t>12419</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -8319,12 +8319,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,87%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,93%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8339,12 +8339,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>6047</t>
+          <t>5934</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13512</t>
+          <t>13948</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -8354,12 +8354,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,26%</t>
         </is>
       </c>
     </row>
@@ -8382,12 +8382,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>6881</t>
+          <t>7264</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17622</t>
+          <t>17840</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -8397,12 +8397,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,65%</t>
+          <t>4,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>11,9%</t>
+          <t>12,05%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8417,12 +8417,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11499</t>
+          <t>11652</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20853</t>
+          <t>20950</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -8432,12 +8432,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,42%</t>
+          <t>6,5%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,64%</t>
+          <t>11,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8452,12 +8452,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20691</t>
+          <t>20958</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35224</t>
+          <t>35474</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -8467,12 +8467,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,32%</t>
+          <t>6,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,76%</t>
+          <t>10,84%</t>
         </is>
       </c>
     </row>
@@ -8495,12 +8495,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>128873</t>
+          <t>128408</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>139903</t>
+          <t>139818</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -8510,12 +8510,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>87,03%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>94,48%</t>
+          <t>94,42%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8530,12 +8530,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>149231</t>
+          <t>149094</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>160689</t>
+          <t>160390</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -8545,12 +8545,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>83,29%</t>
+          <t>83,22%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>89,69%</t>
+          <t>89,52%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8565,12 +8565,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>282170</t>
+          <t>281771</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>297899</t>
+          <t>297673</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -8580,12 +8580,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>86,23%</t>
+          <t>86,1%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>91,03%</t>
+          <t>90,96%</t>
         </is>
       </c>
     </row>
@@ -8725,12 +8725,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1407</t>
+          <t>1470</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7263</t>
+          <t>7662</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -8740,12 +8740,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,79%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8760,12 +8760,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6377</t>
+          <t>6523</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15496</t>
+          <t>16054</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -8775,12 +8775,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,98%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,34%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8795,12 +8795,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>9355</t>
+          <t>9489</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>20476</t>
+          <t>20165</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -8810,12 +8810,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,4%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -8838,12 +8838,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2309</t>
+          <t>2440</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9854</t>
+          <t>10029</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -8853,12 +8853,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,26%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8873,12 +8873,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17146</t>
+          <t>17562</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>30993</t>
+          <t>30265</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -8888,12 +8888,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>7,84%</t>
+          <t>8,03%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>13,84%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8908,12 +8908,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>22238</t>
+          <t>21731</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>37079</t>
+          <t>37405</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -8923,12 +8923,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>5,87%</t>
+          <t>5,74%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,87%</t>
         </is>
       </c>
     </row>
@@ -8951,12 +8951,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>146281</t>
+          <t>145548</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>155374</t>
+          <t>154813</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -8966,12 +8966,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>91,36%</t>
+          <t>90,9%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,04%</t>
+          <t>96,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8986,12 +8986,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>176381</t>
+          <t>177001</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>192184</t>
+          <t>192091</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -9001,12 +9001,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>80,63%</t>
+          <t>80,92%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,86%</t>
+          <t>87,81%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9021,12 +9021,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>325812</t>
+          <t>326798</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>344248</t>
+          <t>345051</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -9036,12 +9036,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>86,0%</t>
+          <t>86,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>90,86%</t>
+          <t>91,08%</t>
         </is>
       </c>
     </row>
@@ -9186,7 +9186,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5114</t>
+          <t>5847</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>4,27%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9216,12 +9216,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1617</t>
+          <t>1339</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>23575</t>
+          <t>21852</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -9231,12 +9231,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,45%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,54%</t>
+          <t>6,07%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9251,12 +9251,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2294</t>
+          <t>2316</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>18567</t>
+          <t>19305</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -9266,12 +9266,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,73%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -9294,12 +9294,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2210</t>
+          <t>2295</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10682</t>
+          <t>10767</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -9309,12 +9309,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,61%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,8%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9329,12 +9329,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>3968</t>
+          <t>4153</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>39901</t>
+          <t>38307</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -9344,12 +9344,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,15%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>11,08%</t>
+          <t>10,63%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9364,12 +9364,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5897</t>
+          <t>5118</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>38645</t>
+          <t>37654</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -9379,12 +9379,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,19%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,77%</t>
+          <t>7,57%</t>
         </is>
       </c>
     </row>
@@ -9407,12 +9407,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>125169</t>
+          <t>125190</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>134314</t>
+          <t>134240</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -9422,12 +9422,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,41%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,07%</t>
+          <t>98,02%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9442,12 +9442,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>300461</t>
+          <t>301909</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>354727</t>
+          <t>353711</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -9457,12 +9457,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,4%</t>
+          <t>83,8%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,47%</t>
+          <t>98,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9477,12 +9477,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>443007</t>
+          <t>443514</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>487870</t>
+          <t>487930</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -9492,12 +9492,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,1%</t>
+          <t>89,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,12%</t>
+          <t>98,13%</t>
         </is>
       </c>
     </row>
@@ -9637,12 +9637,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>628</t>
+          <t>663</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>5916</t>
+          <t>6137</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -9652,12 +9652,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,31%</t>
+          <t>0,32%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,99%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9672,12 +9672,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6874</t>
+          <t>6901</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>16632</t>
+          <t>17245</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -9687,12 +9687,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,05%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9707,12 +9707,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>9393</t>
+          <t>8762</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21196</t>
+          <t>20197</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -9722,12 +9722,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,83%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>4,21%</t>
         </is>
       </c>
     </row>
@@ -9750,12 +9750,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5402</t>
+          <t>5223</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>14499</t>
+          <t>15294</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -9765,12 +9765,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,07%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9785,12 +9785,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15655</t>
+          <t>15649</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29068</t>
+          <t>29336</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -9805,7 +9805,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,57%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9820,12 +9820,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23231</t>
+          <t>23957</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>41157</t>
+          <t>40768</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -9835,12 +9835,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,84%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>8,49%</t>
         </is>
       </c>
     </row>
@@ -9863,12 +9863,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>187430</t>
+          <t>186388</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>197657</t>
+          <t>198018</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -9878,12 +9878,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>91,42%</t>
+          <t>90,91%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>96,4%</t>
+          <t>96,58%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9898,12 +9898,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>233031</t>
+          <t>232931</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>249340</t>
+          <t>248935</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>84,73%</t>
+          <t>84,69%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>90,66%</t>
+          <t>90,51%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9933,12 +9933,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>424078</t>
+          <t>424057</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>444366</t>
+          <t>443646</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -9948,12 +9948,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>88,34%</t>
+          <t>88,33%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>92,56%</t>
+          <t>92,41%</t>
         </is>
       </c>
     </row>
@@ -10093,12 +10093,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4691</t>
+          <t>4720</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13556</t>
+          <t>13120</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -10108,12 +10108,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10128,12 +10128,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21679</t>
+          <t>18716</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>51712</t>
+          <t>51530</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -10143,12 +10143,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,1%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10163,12 +10163,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>31373</t>
+          <t>30422</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>60004</t>
+          <t>59125</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -10178,12 +10178,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,56%</t>
+          <t>3,51%</t>
         </is>
       </c>
     </row>
@@ -10206,12 +10206,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>23421</t>
+          <t>23569</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>41512</t>
+          <t>41782</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -10221,12 +10221,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,43%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>39463</t>
+          <t>37360</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>99852</t>
+          <t>99583</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -10256,12 +10256,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,66%</t>
+          <t>9,64%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10276,12 +10276,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>72172</t>
+          <t>71708</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>131033</t>
+          <t>130360</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -10291,12 +10291,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,74%</t>
         </is>
       </c>
     </row>
@@ -10319,12 +10319,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>599635</t>
+          <t>598789</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>619919</t>
+          <t>619100</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -10334,12 +10334,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>92,23%</t>
+          <t>92,1%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>95,35%</t>
+          <t>95,22%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10354,12 +10354,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>885540</t>
+          <t>885913</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>974576</t>
+          <t>976059</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -10369,12 +10369,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>85,71%</t>
+          <t>85,74%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>94,33%</t>
+          <t>94,47%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10389,12 +10389,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1498585</t>
+          <t>1499521</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1580854</t>
+          <t>1581375</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -10404,12 +10404,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>89,02%</t>
+          <t>89,08%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>93,91%</t>
+          <t>93,94%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/Q5404-Habitat-trans_orig.xlsx
+++ b/data/trans_orig/Q5404-Habitat-trans_orig.xlsx
@@ -738,7 +738,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7543</t>
+          <t>5710</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>6,56%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>3417</t>
+          <t>3446</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>15462</t>
+          <t>15343</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>10,34%</t>
+          <t>10,26%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4926</t>
+          <t>4443</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17947</t>
+          <t>18859</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>6,78%</t>
+          <t>7,13%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>5594</t>
+          <t>5349</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>18082</t>
+          <t>16099</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,87%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>15,73%</t>
+          <t>14,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1976</t>
+          <t>1961</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>11862</t>
+          <t>12372</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,31%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>7,93%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8656</t>
+          <t>9360</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23975</t>
+          <t>25084</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>3,27%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>9,06%</t>
+          <t>9,48%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>95485</t>
+          <t>96125</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>107786</t>
+          <t>107873</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>83,59%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>93,74%</t>
+          <t>93,81%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>127274</t>
+          <t>127674</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>142792</t>
+          <t>142541</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>85,11%</t>
+          <t>85,38%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>95,49%</t>
+          <t>95,32%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>228551</t>
+          <t>228261</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>247915</t>
+          <t>247253</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>86,4%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>93,72%</t>
+          <t>93,47%</t>
         </is>
       </c>
     </row>
@@ -1194,7 +1194,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>6348</t>
+          <t>6335</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1209,7 +1209,7 @@
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,35%</t>
+          <t>4,34%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>2310</t>
+          <t>2051</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>15056</t>
+          <t>12470</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>1,26%</t>
+          <t>1,12%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>8,24%</t>
+          <t>6,83%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>3182</t>
+          <t>3583</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>14646</t>
+          <t>15659</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>0,97%</t>
+          <t>1,09%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>4,46%</t>
+          <t>4,77%</t>
         </is>
       </c>
     </row>
@@ -1302,12 +1302,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>910</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>8668</t>
+          <t>9074</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1317,12 +1317,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,94%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1337,12 +1337,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>3528</t>
+          <t>3395</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>17117</t>
+          <t>16308</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1352,12 +1352,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>1,93%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -1372,12 +1372,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>6561</t>
+          <t>6575</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>21727</t>
+          <t>22728</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>6,61%</t>
+          <t>6,92%</t>
         </is>
       </c>
     </row>
@@ -1415,12 +1415,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>133781</t>
+          <t>134319</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>143244</t>
+          <t>144061</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1430,12 +1430,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>91,7%</t>
+          <t>92,07%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>98,19%</t>
+          <t>98,75%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1450,12 +1450,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>158122</t>
+          <t>159523</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>174721</t>
+          <t>175507</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1465,12 +1465,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>86,56%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,64%</t>
+          <t>96,07%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1485,12 +1485,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>298957</t>
+          <t>298104</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>317003</t>
+          <t>316520</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1500,12 +1500,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>90,99%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>96,48%</t>
+          <t>96,33%</t>
         </is>
       </c>
     </row>
@@ -1645,12 +1645,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>751</t>
+          <t>765</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>10216</t>
+          <t>10086</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1660,12 +1660,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>9,79%</t>
+          <t>9,66%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1680,12 +1680,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2393</t>
+          <t>2874</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>13096</t>
+          <t>12989</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1695,12 +1695,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>9,56%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1715,12 +1715,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4896</t>
+          <t>4769</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>18404</t>
+          <t>19306</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1730,12 +1730,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>8,04%</t>
         </is>
       </c>
     </row>
@@ -1763,7 +1763,7 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>5708</t>
+          <t>5741</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1778,7 +1778,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1793,12 +1793,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>2679</t>
+          <t>1945</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>12395</t>
+          <t>12039</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1808,12 +1808,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,97%</t>
+          <t>1,43%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>8,86%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1828,12 +1828,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>3689</t>
+          <t>2937</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>14389</t>
+          <t>13683</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1843,12 +1843,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>5,7%</t>
         </is>
       </c>
     </row>
@@ -1871,12 +1871,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>92639</t>
+          <t>91668</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>102534</t>
+          <t>102493</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1886,12 +1886,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,76%</t>
+          <t>87,83%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,24%</t>
+          <t>98,2%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1906,12 +1906,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>114901</t>
+          <t>116212</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>129141</t>
+          <t>129597</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1921,12 +1921,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>84,58%</t>
+          <t>85,54%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>95,06%</t>
+          <t>95,4%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1941,12 +1941,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>212020</t>
+          <t>212353</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>229371</t>
+          <t>229504</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1956,12 +1956,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>88,26%</t>
+          <t>88,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>95,48%</t>
+          <t>95,54%</t>
         </is>
       </c>
     </row>
@@ -2101,12 +2101,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>837</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>7609</t>
+          <t>7783</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2121,7 +2121,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>5,55%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2136,12 +2136,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>4010</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>15889</t>
+          <t>15831</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2151,12 +2151,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,92%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>7,61%</t>
+          <t>7,58%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>6319</t>
+          <t>6201</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>19834</t>
+          <t>19638</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2186,12 +2186,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,79%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,73%</t>
+          <t>5,68%</t>
         </is>
       </c>
     </row>
@@ -2214,12 +2214,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>2440</t>
+          <t>1707</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>10861</t>
+          <t>9897</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2229,12 +2229,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,92%</t>
+          <t>7,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2249,12 +2249,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>8033</t>
+          <t>8119</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22737</t>
+          <t>23212</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2264,12 +2264,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,85%</t>
+          <t>3,89%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,89%</t>
+          <t>11,12%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2284,12 +2284,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>12126</t>
+          <t>12374</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>29394</t>
+          <t>30100</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2299,12 +2299,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>3,5%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,7%</t>
         </is>
       </c>
     </row>
@@ -2327,12 +2327,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>122947</t>
+          <t>123099</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>132988</t>
+          <t>133061</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2342,12 +2342,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,71%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,97%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2362,12 +2362,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>176313</t>
+          <t>174364</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>193704</t>
+          <t>194335</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2377,12 +2377,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>84,45%</t>
+          <t>83,52%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>92,78%</t>
+          <t>93,08%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2397,12 +2397,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>303743</t>
+          <t>303426</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>324125</t>
+          <t>324628</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2412,12 +2412,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>87,79%</t>
+          <t>87,7%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>93,68%</t>
+          <t>93,82%</t>
         </is>
       </c>
     </row>
@@ -2557,12 +2557,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5392</t>
+          <t>5365</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>19218</t>
+          <t>18854</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2577,7 +2577,7 @@
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2592,12 +2592,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>19259</t>
+          <t>19584</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>40464</t>
+          <t>40052</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2607,12 +2607,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,85%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,92%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>28782</t>
+          <t>28488</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>55118</t>
+          <t>52952</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2642,12 +2642,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>2,44%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>4,67%</t>
+          <t>4,49%</t>
         </is>
       </c>
     </row>
@@ -2670,12 +2670,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13308</t>
+          <t>14372</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>29910</t>
+          <t>31579</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -2685,12 +2685,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,28%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -2705,12 +2705,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>24356</t>
+          <t>23392</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>47509</t>
+          <t>46644</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -2720,12 +2720,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>7,02%</t>
+          <t>6,89%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -2740,12 +2740,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>42763</t>
+          <t>41076</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>70900</t>
+          <t>70642</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -2755,12 +2755,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>6,01%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -2783,12 +2783,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>459469</t>
+          <t>458962</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>480326</t>
+          <t>479663</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2798,12 +2798,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,34%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>95,59%</t>
+          <t>95,46%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2818,12 +2818,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>597520</t>
+          <t>598847</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>628825</t>
+          <t>628560</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2833,12 +2833,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>92,91%</t>
+          <t>92,87%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2853,12 +2853,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1062788</t>
+          <t>1066793</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1102062</t>
+          <t>1104239</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2868,12 +2868,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>90,12%</t>
+          <t>90,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>93,45%</t>
+          <t>93,63%</t>
         </is>
       </c>
     </row>
@@ -3245,12 +3245,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1920</t>
+          <t>1976</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10970</t>
+          <t>11022</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3260,12 +3260,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,42%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,9%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3280,12 +3280,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>4234</t>
+          <t>4215</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>16275</t>
+          <t>15965</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3295,12 +3295,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>9,76%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3315,12 +3315,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>7544</t>
+          <t>7454</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>21920</t>
+          <t>22096</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3330,12 +3330,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,43%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>7,16%</t>
+          <t>7,21%</t>
         </is>
       </c>
     </row>
@@ -3363,7 +3363,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>13236</t>
+          <t>12258</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3378,7 +3378,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>8,78%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3393,12 +3393,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>10450</t>
+          <t>10312</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>26918</t>
+          <t>25688</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3408,12 +3408,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>16,14%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3428,12 +3428,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>12957</t>
+          <t>12741</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>31007</t>
+          <t>32482</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3443,12 +3443,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>4,23%</t>
+          <t>4,16%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,12%</t>
+          <t>10,6%</t>
         </is>
       </c>
     </row>
@@ -3471,12 +3471,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>122156</t>
+          <t>122370</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>136193</t>
+          <t>136438</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3486,12 +3486,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>97,6%</t>
+          <t>97,77%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3506,12 +3506,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>130335</t>
+          <t>130869</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>149234</t>
+          <t>149381</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3521,12 +3521,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>78,14%</t>
+          <t>78,46%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,56%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3541,12 +3541,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>261199</t>
+          <t>260218</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>282053</t>
+          <t>282362</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -3556,12 +3556,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,17%</t>
         </is>
       </c>
     </row>
@@ -3701,12 +3701,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>2244</t>
+          <t>2162</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>13842</t>
+          <t>12765</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -3716,12 +3716,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,45%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>8,94%</t>
+          <t>8,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -3736,12 +3736,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>8762</t>
+          <t>8947</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>23876</t>
+          <t>24652</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -3751,12 +3751,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>4,58%</t>
+          <t>4,67%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>12,47%</t>
+          <t>12,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -3771,12 +3771,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>14074</t>
+          <t>13938</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>32253</t>
+          <t>32461</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -3786,12 +3786,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>4,06%</t>
+          <t>4,02%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>9,31%</t>
+          <t>9,37%</t>
         </is>
       </c>
     </row>
@@ -3814,12 +3814,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7849</t>
+          <t>7855</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>24898</t>
+          <t>24379</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -3834,7 +3834,7 @@
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>16,08%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -3849,12 +3849,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17511</t>
+          <t>17941</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>39654</t>
+          <t>37477</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -3864,12 +3864,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>20,72%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -3884,12 +3884,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>29914</t>
+          <t>29877</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>55473</t>
+          <t>56507</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -3899,12 +3899,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,63%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>16,02%</t>
+          <t>16,32%</t>
         </is>
       </c>
     </row>
@@ -3927,12 +3927,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>123195</t>
+          <t>124098</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>141616</t>
+          <t>141671</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3942,12 +3942,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>80,13%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>91,44%</t>
+          <t>91,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3962,12 +3962,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>136849</t>
+          <t>137420</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>161698</t>
+          <t>160693</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3977,12 +3977,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>71,49%</t>
+          <t>71,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>84,47%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3997,12 +3997,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>266866</t>
+          <t>268819</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>297174</t>
+          <t>299035</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4012,12 +4012,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>85,81%</t>
+          <t>86,35%</t>
         </is>
       </c>
     </row>
@@ -4157,12 +4157,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>2123</t>
+          <t>2133</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>15309</t>
+          <t>13947</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4172,12 +4172,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,06%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>14,78%</t>
+          <t>13,46%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4192,12 +4192,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>4798</t>
+          <t>4415</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>18567</t>
+          <t>18849</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4207,12 +4207,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,13%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>13,17%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4227,12 +4227,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>8533</t>
+          <t>9424</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>27817</t>
+          <t>26626</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4242,12 +4242,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>3,49%</t>
+          <t>3,85%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>11,37%</t>
+          <t>10,88%</t>
         </is>
       </c>
     </row>
@@ -4270,12 +4270,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>956</t>
+          <t>965</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>8629</t>
+          <t>7697</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4285,12 +4285,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>8,33%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4305,12 +4305,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>9610</t>
+          <t>8737</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>25764</t>
+          <t>25525</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4320,12 +4320,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>6,81%</t>
+          <t>6,2%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>18,27%</t>
+          <t>18,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4340,12 +4340,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>11515</t>
+          <t>10855</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28627</t>
+          <t>28093</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4355,12 +4355,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,71%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,7%</t>
+          <t>11,48%</t>
         </is>
       </c>
     </row>
@@ -4383,12 +4383,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>85132</t>
+          <t>86227</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>99529</t>
+          <t>99345</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4398,12 +4398,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>82,18%</t>
+          <t>83,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>96,07%</t>
+          <t>95,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4418,12 +4418,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>104093</t>
+          <t>104389</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>123719</t>
+          <t>123840</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>73,81%</t>
+          <t>74,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>87,73%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4453,12 +4453,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>195333</t>
+          <t>197071</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>219590</t>
+          <t>219972</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>80,56%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,77%</t>
+          <t>89,93%</t>
         </is>
       </c>
     </row>
@@ -4613,12 +4613,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>2018</t>
+          <t>1969</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>11516</t>
+          <t>11006</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -4628,12 +4628,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,22%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>6,81%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -4648,12 +4648,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6375</t>
+          <t>7010</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20543</t>
+          <t>20731</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -4663,12 +4663,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -4683,12 +4683,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>10394</t>
+          <t>10510</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>26759</t>
+          <t>27441</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -4698,12 +4698,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>2,56%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>6,6%</t>
+          <t>6,77%</t>
         </is>
       </c>
     </row>
@@ -4726,12 +4726,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>4040</t>
+          <t>4046</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>17468</t>
+          <t>17504</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -4746,7 +4746,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>10,81%</t>
+          <t>10,83%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -4761,12 +4761,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9064</t>
+          <t>9900</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>24631</t>
+          <t>26384</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>3,72%</t>
+          <t>4,06%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,1%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -4796,12 +4796,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17376</t>
+          <t>16242</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>37825</t>
+          <t>37821</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -4811,7 +4811,7 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,29%</t>
+          <t>4,01%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
@@ -4839,12 +4839,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>137806</t>
+          <t>137684</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>154044</t>
+          <t>153255</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -4854,12 +4854,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>85,19%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>95,32%</t>
+          <t>94,83%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -4874,12 +4874,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>204006</t>
+          <t>203234</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>223756</t>
+          <t>224155</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>83,69%</t>
+          <t>83,38%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>91,8%</t>
+          <t>91,96%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -4909,12 +4909,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>347589</t>
+          <t>347925</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>373201</t>
+          <t>374762</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>85,83%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>92,07%</t>
+          <t>92,45%</t>
         </is>
       </c>
     </row>
@@ -5069,12 +5069,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>13843</t>
+          <t>15312</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>33816</t>
+          <t>36255</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5084,12 +5084,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,74%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>6,04%</t>
+          <t>6,48%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5104,12 +5104,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>34137</t>
+          <t>32880</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>60379</t>
+          <t>60027</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>8,08%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5139,12 +5139,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>54167</t>
+          <t>54289</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>87626</t>
+          <t>88554</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,17%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>6,73%</t>
+          <t>6,8%</t>
         </is>
       </c>
     </row>
@@ -5182,12 +5182,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>19699</t>
+          <t>18926</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>44532</t>
+          <t>43883</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -5197,12 +5197,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,52%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>7,96%</t>
+          <t>7,84%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -5217,12 +5217,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>60606</t>
+          <t>58925</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>95705</t>
+          <t>94214</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>8,16%</t>
+          <t>7,93%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>12,88%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -5252,12 +5252,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>87021</t>
+          <t>87263</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>128747</t>
+          <t>126626</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>6,7%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>9,88%</t>
+          <t>9,72%</t>
         </is>
       </c>
     </row>
@@ -5295,12 +5295,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>490400</t>
+          <t>488971</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>520596</t>
+          <t>520483</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5310,12 +5310,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>87,63%</t>
+          <t>87,37%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>93,02%</t>
+          <t>93,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5330,12 +5330,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>598491</t>
+          <t>599802</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>639661</t>
+          <t>642328</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5345,12 +5345,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>86,09%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5365,12 +5365,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1098264</t>
+          <t>1101853</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1152995</t>
+          <t>1151729</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5380,12 +5380,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>84,31%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>88,51%</t>
+          <t>88,42%</t>
         </is>
       </c>
     </row>
@@ -5757,12 +5757,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>1764</t>
+          <t>1752</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>10272</t>
+          <t>10354</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5772,12 +5772,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>7,51%</t>
+          <t>7,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5792,12 +5792,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>1119</t>
+          <t>1185</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>11062</t>
+          <t>10864</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5807,12 +5807,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>0,65%</t>
+          <t>0,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,38%</t>
+          <t>6,27%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5827,12 +5827,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>4970</t>
+          <t>5321</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>17430</t>
+          <t>17930</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5842,12 +5842,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,6%</t>
+          <t>1,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,78%</t>
         </is>
       </c>
     </row>
@@ -5870,12 +5870,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1580</t>
+          <t>1593</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10120</t>
+          <t>8839</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5885,12 +5885,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>7,4%</t>
+          <t>6,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5905,12 +5905,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>4562</t>
+          <t>4622</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>17580</t>
+          <t>18217</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,67%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>10,14%</t>
+          <t>10,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5940,12 +5940,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>8356</t>
+          <t>8444</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>23757</t>
+          <t>23770</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5955,7 +5955,7 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
@@ -5983,12 +5983,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>121221</t>
+          <t>121149</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>131858</t>
+          <t>131991</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5998,12 +5998,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>88,65%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>96,43%</t>
+          <t>96,53%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6018,12 +6018,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>149306</t>
+          <t>150724</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>165115</t>
+          <t>165574</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>86,11%</t>
+          <t>86,93%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>95,23%</t>
+          <t>95,49%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -6053,12 +6053,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>275198</t>
+          <t>273864</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>294719</t>
+          <t>293456</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,31%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>95,03%</t>
+          <t>94,63%</t>
         </is>
       </c>
     </row>
@@ -6213,12 +6213,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1673</t>
+          <t>1812</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9818</t>
+          <t>10644</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6228,12 +6228,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>5,95%</t>
+          <t>6,45%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6248,12 +6248,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>1245</t>
+          <t>1258</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>13882</t>
+          <t>13940</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6268,7 +6268,7 @@
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>6,33%</t>
+          <t>6,36%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6283,12 +6283,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>4142</t>
+          <t>4558</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>19958</t>
+          <t>19199</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,19%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,0%</t>
         </is>
       </c>
     </row>
@@ -6326,12 +6326,12 @@
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1651</t>
+          <t>1641</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>9264</t>
+          <t>9222</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6341,12 +6341,12 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>5,62%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -6361,12 +6361,12 @@
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>7279</t>
+          <t>8020</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>23605</t>
+          <t>23385</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>3,32%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>10,77%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -6396,12 +6396,12 @@
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>10503</t>
+          <t>11164</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>29107</t>
+          <t>28264</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="V9" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,91%</t>
         </is>
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>7,58%</t>
+          <t>7,36%</t>
         </is>
       </c>
     </row>
@@ -6439,12 +6439,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>149949</t>
+          <t>148700</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>160575</t>
+          <t>160633</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6454,12 +6454,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>90,15%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>97,35%</t>
+          <t>97,39%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6474,12 +6474,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>189045</t>
+          <t>187730</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>208350</t>
+          <t>207270</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6489,12 +6489,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>95,07%</t>
+          <t>94,57%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6509,12 +6509,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>344171</t>
+          <t>342867</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>366034</t>
+          <t>365808</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6524,12 +6524,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>89,6%</t>
+          <t>89,26%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>95,3%</t>
+          <t>95,24%</t>
         </is>
       </c>
     </row>
@@ -6674,7 +6674,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>4062</t>
+          <t>4078</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6689,7 +6689,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>3,53%</t>
+          <t>3,54%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -6704,12 +6704,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>2616</t>
+          <t>2678</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>14272</t>
+          <t>15365</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,88%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>10,01%</t>
+          <t>10,78%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -6739,12 +6739,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3651</t>
+          <t>3395</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16612</t>
+          <t>16471</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,42%</t>
+          <t>1,32%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>6,45%</t>
+          <t>6,39%</t>
         </is>
       </c>
     </row>
@@ -6782,12 +6782,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2044</t>
+          <t>2511</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>11762</t>
+          <t>11287</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6797,12 +6797,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>10,22%</t>
+          <t>9,81%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6817,12 +6817,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>6421</t>
+          <t>6574</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>21867</t>
+          <t>21171</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6832,12 +6832,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,61%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>15,33%</t>
+          <t>14,85%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6852,12 +6852,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>10803</t>
+          <t>11125</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>28623</t>
+          <t>28891</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6867,12 +6867,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>11,11%</t>
+          <t>11,21%</t>
         </is>
       </c>
     </row>
@@ -6895,12 +6895,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>101966</t>
+          <t>101547</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>112156</t>
+          <t>112111</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6910,12 +6910,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>88,64%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>97,5%</t>
+          <t>97,46%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6930,12 +6930,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>111887</t>
+          <t>111491</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>130666</t>
+          <t>129883</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6945,12 +6945,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,46%</t>
+          <t>78,19%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,63%</t>
+          <t>91,08%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6965,12 +6965,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>219062</t>
+          <t>218720</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>239380</t>
+          <t>239517</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6980,12 +6980,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>85,03%</t>
+          <t>84,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,97%</t>
         </is>
       </c>
     </row>
@@ -7160,12 +7160,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>5008</t>
+          <t>5147</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>20830</t>
+          <t>21039</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -7175,12 +7175,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,06%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>8,58%</t>
+          <t>8,67%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -7195,12 +7195,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>5169</t>
+          <t>5066</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>21774</t>
+          <t>20911</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -7210,12 +7210,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,24%</t>
+          <t>1,21%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>5,22%</t>
+          <t>5,01%</t>
         </is>
       </c>
     </row>
@@ -7238,12 +7238,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>3098</t>
+          <t>3039</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>13577</t>
+          <t>13489</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -7253,12 +7253,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,77%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,78%</t>
+          <t>7,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -7273,12 +7273,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>5854</t>
+          <t>5866</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>21582</t>
+          <t>21085</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -7288,12 +7288,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,41%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>8,89%</t>
+          <t>8,68%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -7308,12 +7308,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>11703</t>
+          <t>11514</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>29968</t>
+          <t>30350</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -7323,12 +7323,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,18%</t>
+          <t>7,27%</t>
         </is>
       </c>
     </row>
@@ -7351,12 +7351,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>161041</t>
+          <t>161129</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>171520</t>
+          <t>171579</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -7366,12 +7366,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>92,22%</t>
+          <t>92,28%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>98,23%</t>
+          <t>98,26%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -7386,12 +7386,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>205816</t>
+          <t>207058</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>228534</t>
+          <t>228052</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -7401,12 +7401,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>84,77%</t>
+          <t>85,29%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>94,13%</t>
+          <t>93,93%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -7421,12 +7421,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>373446</t>
+          <t>374390</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>397018</t>
+          <t>396887</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -7436,12 +7436,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>95,12%</t>
+          <t>95,09%</t>
         </is>
       </c>
     </row>
@@ -7581,12 +7581,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>5304</t>
+          <t>5197</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>17202</t>
+          <t>17404</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -7596,12 +7596,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,91%</t>
+          <t>2,94%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -7616,12 +7616,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>18178</t>
+          <t>18566</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>42735</t>
+          <t>43157</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -7631,12 +7631,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>2,34%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>5,49%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -7651,12 +7651,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>26846</t>
+          <t>26693</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>54224</t>
+          <t>53192</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -7666,12 +7666,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,96%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,88%</t>
         </is>
       </c>
     </row>
@@ -7694,12 +7694,12 @@
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>13687</t>
+          <t>13897</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>30963</t>
+          <t>31637</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -7709,12 +7709,12 @@
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>5,24%</t>
+          <t>5,35%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -7729,12 +7729,12 @@
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>35940</t>
+          <t>35638</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>67382</t>
+          <t>64932</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -7744,12 +7744,12 @@
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>4,62%</t>
+          <t>4,58%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -7764,12 +7764,12 @@
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>53558</t>
+          <t>55245</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>88741</t>
+          <t>89343</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -7779,12 +7779,12 @@
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>3,91%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,52%</t>
         </is>
       </c>
     </row>
@@ -7807,12 +7807,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>549165</t>
+          <t>548007</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>568723</t>
+          <t>568650</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -7822,12 +7822,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>92,87%</t>
+          <t>92,67%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,16%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -7842,12 +7842,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>679022</t>
+          <t>679359</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>717207</t>
+          <t>717071</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -7857,12 +7857,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>87,29%</t>
+          <t>87,33%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>92,19%</t>
+          <t>92,18%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -7877,12 +7877,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1240146</t>
+          <t>1236976</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1282104</t>
+          <t>1279168</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -7892,12 +7892,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>90,57%</t>
+          <t>90,34%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>93,63%</t>
+          <t>93,42%</t>
         </is>
       </c>
     </row>
@@ -8264,32 +8264,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>1531</t>
+          <t>1549</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>358</t>
+          <t>354</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4142</t>
+          <t>3719</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,8%</t>
+          <t>2,28%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -8299,32 +8299,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>7830</t>
+          <t>8244</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>5147</t>
+          <t>4948</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>12419</t>
+          <t>12729</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>4,37%</t>
+          <t>4,32%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,59%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -8334,32 +8334,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>9362</t>
+          <t>9793</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>5934</t>
+          <t>6270</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>13948</t>
+          <t>14980</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>2,86%</t>
+          <t>2,76%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,77%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>4,23%</t>
         </is>
       </c>
     </row>
@@ -8377,32 +8377,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>11594</t>
+          <t>12202</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>7264</t>
+          <t>7330</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>17840</t>
+          <t>18454</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>4,91%</t>
+          <t>4,49%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>12,05%</t>
+          <t>11,3%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -8412,32 +8412,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>15878</t>
+          <t>17115</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>11652</t>
+          <t>12352</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>20950</t>
+          <t>23525</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>8,86%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>6,5%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>11,69%</t>
+          <t>12,31%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -8447,32 +8447,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>27471</t>
+          <t>29317</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>20958</t>
+          <t>22589</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>35474</t>
+          <t>37357</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>8,39%</t>
+          <t>8,27%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>10,84%</t>
+          <t>10,54%</t>
         </is>
       </c>
     </row>
@@ -8490,32 +8490,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>134958</t>
+          <t>149563</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>128408</t>
+          <t>142971</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>139818</t>
+          <t>154240</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>91,14%</t>
+          <t>91,58%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>87,54%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>94,42%</t>
+          <t>94,44%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -8525,32 +8525,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>155455</t>
+          <t>165670</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>149094</t>
+          <t>158414</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>160390</t>
+          <t>171215</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>86,77%</t>
+          <t>86,73%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>83,22%</t>
+          <t>82,93%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>89,52%</t>
+          <t>89,63%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -8560,32 +8560,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>290413</t>
+          <t>315233</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>281771</t>
+          <t>306339</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>297673</t>
+          <t>323040</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>86,1%</t>
+          <t>86,45%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>90,96%</t>
+          <t>91,17%</t>
         </is>
       </c>
     </row>
@@ -8603,17 +8603,17 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>148083</t>
+          <t>163314</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -8638,17 +8638,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>179163</t>
+          <t>191029</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>179163</t>
+          <t>191029</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>179163</t>
+          <t>191029</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -8673,17 +8673,17 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>327246</t>
+          <t>354343</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>327246</t>
+          <t>354343</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>327246</t>
+          <t>354343</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -8720,32 +8720,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>3480</t>
+          <t>3560</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>1470</t>
+          <t>1435</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>7662</t>
+          <t>7062</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,0%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>4,79%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -8755,32 +8755,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>10498</t>
+          <t>11483</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>6523</t>
+          <t>7465</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>16054</t>
+          <t>18027</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>4,8%</t>
+          <t>4,74%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>2,98%</t>
+          <t>3,08%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>7,34%</t>
+          <t>7,45%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -8790,32 +8790,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>13978</t>
+          <t>15043</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>9489</t>
+          <t>10035</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>20165</t>
+          <t>22054</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>3,69%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>5,25%</t>
         </is>
       </c>
     </row>
@@ -8833,32 +8833,32 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>5410</t>
+          <t>6161</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>2440</t>
+          <t>3012</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>10029</t>
+          <t>11922</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>6,26%</t>
+          <t>6,69%</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -8868,32 +8868,32 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>23268</t>
+          <t>25202</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>17562</t>
+          <t>19016</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>30265</t>
+          <t>32994</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="O9" s="2" t="inlineStr">
         <is>
-          <t>8,03%</t>
+          <t>7,86%</t>
         </is>
       </c>
       <c r="P9" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>13,63%</t>
         </is>
       </c>
       <c r="Q9" s="2" t="inlineStr">
@@ -8903,22 +8903,22 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>28678</t>
+          <t>31363</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>21731</t>
+          <t>24126</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>37405</t>
+          <t>40162</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>7,46%</t>
         </is>
       </c>
       <c r="V9" s="2" t="inlineStr">
@@ -8928,7 +8928,7 @@
       </c>
       <c r="W9" s="2" t="inlineStr">
         <is>
-          <t>9,87%</t>
+          <t>9,56%</t>
         </is>
       </c>
     </row>
@@ -8946,32 +8946,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>151224</t>
+          <t>168483</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>145548</t>
+          <t>162487</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>154813</t>
+          <t>172628</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>94,45%</t>
+          <t>94,55%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>90,9%</t>
+          <t>91,18%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>96,69%</t>
+          <t>96,87%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -8981,32 +8981,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>184980</t>
+          <t>205355</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>177001</t>
+          <t>195758</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>192091</t>
+          <t>212521</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,84%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>80,92%</t>
+          <t>80,88%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,81%</t>
+          <t>87,8%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -9016,32 +9016,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>336203</t>
+          <t>373837</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>326798</t>
+          <t>363553</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>345051</t>
+          <t>383023</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>88,74%</t>
+          <t>88,96%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>86,26%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>91,08%</t>
+          <t>91,14%</t>
         </is>
       </c>
     </row>
@@ -9059,17 +9059,17 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>160114</t>
+          <t>178204</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -9094,17 +9094,17 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>218746</t>
+          <t>242040</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>218746</t>
+          <t>242040</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>218746</t>
+          <t>242040</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -9129,17 +9129,17 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>378860</t>
+          <t>420243</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>378860</t>
+          <t>420243</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>378860</t>
+          <t>420243</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -9176,7 +9176,7 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>858</t>
+          <t>929</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -9186,12 +9186,12 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>5847</t>
+          <t>4677</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
@@ -9201,7 +9201,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -9211,32 +9211,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>8326</t>
+          <t>9109</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1339</t>
+          <t>4960</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>21852</t>
+          <t>15671</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>5,21%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>2,84%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,07%</t>
+          <t>8,96%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -9246,32 +9246,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>9184</t>
+          <t>10038</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>2316</t>
+          <t>5642</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>19305</t>
+          <t>16829</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,47%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>3,88%</t>
+          <t>5,03%</t>
         </is>
       </c>
     </row>
@@ -9289,32 +9289,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>5501</t>
+          <t>6016</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>2295</t>
+          <t>2704</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10767</t>
+          <t>12203</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>4,02%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,69%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>7,86%</t>
+          <t>7,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -9324,32 +9324,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>15023</t>
+          <t>15819</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4153</t>
+          <t>10524</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>38307</t>
+          <t>21814</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>4,17%</t>
+          <t>9,04%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>6,02%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>10,63%</t>
+          <t>12,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -9359,32 +9359,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>20524</t>
+          <t>21835</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>5118</t>
+          <t>15100</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>37654</t>
+          <t>29522</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>6,52%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>4,51%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>7,57%</t>
+          <t>8,82%</t>
         </is>
       </c>
     </row>
@@ -9402,32 +9402,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>130593</t>
+          <t>152840</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>125190</t>
+          <t>146207</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>134240</t>
+          <t>156570</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>95,36%</t>
+          <t>95,65%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>91,41%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>98,02%</t>
+          <t>97,99%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -9437,32 +9437,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>336907</t>
+          <t>149982</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>301909</t>
+          <t>141947</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>353711</t>
+          <t>156976</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>93,52%</t>
+          <t>85,75%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>83,8%</t>
+          <t>81,15%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>98,18%</t>
+          <t>89,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -9472,32 +9472,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>467501</t>
+          <t>302821</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>443514</t>
+          <t>293486</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>487930</t>
+          <t>311072</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>94,03%</t>
+          <t>90,48%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>89,2%</t>
+          <t>87,69%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>98,13%</t>
+          <t>92,94%</t>
         </is>
       </c>
     </row>
@@ -9515,17 +9515,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>136952</t>
+          <t>159785</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>136952</t>
+          <t>159785</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>136952</t>
+          <t>159785</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -9550,17 +9550,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>360256</t>
+          <t>174909</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>360256</t>
+          <t>174909</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>360256</t>
+          <t>174909</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -9585,17 +9585,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>497209</t>
+          <t>334694</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>497209</t>
+          <t>334694</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>497209</t>
+          <t>334694</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -9632,32 +9632,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>2524</t>
+          <t>2439</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>663</t>
+          <t>646</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>6137</t>
+          <t>5586</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>2,99%</t>
+          <t>2,6%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -9667,32 +9667,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>11276</t>
+          <t>12148</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6901</t>
+          <t>7547</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>17245</t>
+          <t>18615</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>4,1%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>6,27%</t>
+          <t>6,32%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -9702,32 +9702,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>13800</t>
+          <t>14587</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>8762</t>
+          <t>9824</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>20197</t>
+          <t>22032</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,86%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>4,21%</t>
+          <t>4,32%</t>
         </is>
       </c>
     </row>
@@ -9745,32 +9745,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9077</t>
+          <t>9862</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5223</t>
+          <t>5681</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>15294</t>
+          <t>16346</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,59%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,46%</t>
+          <t>7,6%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -9780,32 +9780,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>22025</t>
+          <t>24611</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>15649</t>
+          <t>17665</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>29336</t>
+          <t>32589</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8,01%</t>
+          <t>8,35%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,69%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>11,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -9815,32 +9815,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>31103</t>
+          <t>34473</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>23957</t>
+          <t>26234</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>40768</t>
+          <t>44442</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>6,48%</t>
+          <t>6,76%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,15%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,72%</t>
         </is>
       </c>
     </row>
@@ -9858,32 +9858,32 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>193428</t>
+          <t>202788</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>186388</t>
+          <t>196299</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>198018</t>
+          <t>207386</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>94,34%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>90,91%</t>
+          <t>91,26%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>96,58%</t>
+          <t>96,42%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -9893,32 +9893,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>241730</t>
+          <t>257961</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>232931</t>
+          <t>249392</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>248935</t>
+          <t>266700</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>87,89%</t>
+          <t>87,53%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>84,69%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,49%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -9928,32 +9928,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>435158</t>
+          <t>460748</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>424057</t>
+          <t>448612</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>443646</t>
+          <t>470397</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>90,65%</t>
+          <t>90,38%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>88,33%</t>
+          <t>88,0%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>92,41%</t>
+          <t>92,27%</t>
         </is>
       </c>
     </row>
@@ -9971,17 +9971,17 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>205029</t>
+          <t>215089</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>205029</t>
+          <t>215089</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>205029</t>
+          <t>215089</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -10006,17 +10006,17 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>275031</t>
+          <t>294720</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>275031</t>
+          <t>294720</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>275031</t>
+          <t>294720</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -10041,17 +10041,17 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>480060</t>
+          <t>509808</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>480060</t>
+          <t>509808</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>480060</t>
+          <t>509808</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -10088,32 +10088,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>8394</t>
+          <t>8477</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>4720</t>
+          <t>4957</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>13120</t>
+          <t>13978</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>1,29%</t>
+          <t>1,18%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>0,73%</t>
+          <t>0,69%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,95%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -10123,32 +10123,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>37930</t>
+          <t>40984</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>18716</t>
+          <t>32125</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>51530</t>
+          <t>51194</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>3,67%</t>
+          <t>4,54%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>3,56%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -10158,32 +10158,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>46324</t>
+          <t>49461</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>30422</t>
+          <t>39688</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>59125</t>
+          <t>60330</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>3,05%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,45%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>3,51%</t>
+          <t>3,73%</t>
         </is>
       </c>
     </row>
@@ -10201,32 +10201,32 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>31582</t>
+          <t>34242</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>23569</t>
+          <t>25678</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>41782</t>
+          <t>45234</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>4,86%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>6,43%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
@@ -10236,32 +10236,32 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>76194</t>
+          <t>82746</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>37360</t>
+          <t>69870</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>99583</t>
+          <t>97847</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>7,37%</t>
+          <t>9,17%</t>
         </is>
       </c>
       <c r="O21" s="2" t="inlineStr">
         <is>
-          <t>3,62%</t>
+          <t>7,74%</t>
         </is>
       </c>
       <c r="P21" s="2" t="inlineStr">
         <is>
-          <t>9,64%</t>
+          <t>10,84%</t>
         </is>
       </c>
       <c r="Q21" s="2" t="inlineStr">
@@ -10271,32 +10271,32 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>107776</t>
+          <t>116988</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>71708</t>
+          <t>102093</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>130360</t>
+          <t>133945</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
         <is>
-          <t>6,4%</t>
+          <t>7,23%</t>
         </is>
       </c>
       <c r="V21" s="2" t="inlineStr">
         <is>
-          <t>4,26%</t>
+          <t>6,31%</t>
         </is>
       </c>
       <c r="W21" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,27%</t>
         </is>
       </c>
     </row>
@@ -10314,32 +10314,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>610202</t>
+          <t>673672</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>598789</t>
+          <t>661824</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>619100</t>
+          <t>683371</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>94,04%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>92,1%</t>
+          <t>92,38%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>95,22%</t>
+          <t>95,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -10349,32 +10349,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>919073</t>
+          <t>778968</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>885913</t>
+          <t>762906</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>976059</t>
+          <t>794829</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>88,95%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>85,74%</t>
+          <t>84,51%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>94,47%</t>
+          <t>88,05%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -10384,32 +10384,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>1529275</t>
+          <t>1452640</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1499521</t>
+          <t>1433359</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>1581375</t>
+          <t>1470580</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>89,72%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>89,08%</t>
+          <t>88,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>93,94%</t>
+          <t>90,83%</t>
         </is>
       </c>
     </row>
@@ -10427,17 +10427,17 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>650178</t>
+          <t>716391</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -10462,17 +10462,17 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>1033197</t>
+          <t>902698</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1033197</t>
+          <t>902698</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>1033197</t>
+          <t>902698</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -10497,17 +10497,17 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>1683375</t>
+          <t>1619089</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>1683375</t>
+          <t>1619089</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>1683375</t>
+          <t>1619089</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
